--- a/artfynd/A 51024-2024 artfynd.xlsx
+++ b/artfynd/A 51024-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131328330</v>
+        <v>131328338</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560485</v>
+        <v>560289</v>
       </c>
       <c r="R2" t="n">
-        <v>6913922</v>
+        <v>6914052</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -915,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131328338</v>
+        <v>131328330</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,34 +913,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560289</v>
+        <v>560485</v>
       </c>
       <c r="R4" t="n">
-        <v>6914052</v>
+        <v>6913922</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,7 +990,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,7 +1025,7 @@
         <v>131328337</v>
       </c>
       <c r="B5" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>131328334</v>
       </c>
       <c r="B7" t="n">
-        <v>92535</v>
+        <v>92536</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>131328331</v>
       </c>
       <c r="B8" t="n">
-        <v>80385</v>
+        <v>80386</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>131328327</v>
       </c>
       <c r="B9" t="n">
-        <v>92037</v>
+        <v>92038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131328323</v>
+        <v>131328319</v>
       </c>
       <c r="B10" t="n">
-        <v>91809</v>
+        <v>91814</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560332</v>
+        <v>560290</v>
       </c>
       <c r="R10" t="n">
-        <v>6913869</v>
+        <v>6913825</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,10 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131328319</v>
+        <v>131328323</v>
       </c>
       <c r="B11" t="n">
-        <v>91813</v>
+        <v>91810</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1684,21 +1684,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560290</v>
+        <v>560332</v>
       </c>
       <c r="R11" t="n">
-        <v>6913825</v>
+        <v>6913869</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,32 +1780,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131328318</v>
+        <v>131328325</v>
       </c>
       <c r="B12" t="n">
-        <v>5177</v>
+        <v>91814</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1815,10 +1815,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560288</v>
+        <v>560337</v>
       </c>
       <c r="R12" t="n">
-        <v>6913825</v>
+        <v>6913867</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1887,10 +1887,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131328325</v>
+        <v>131328313</v>
       </c>
       <c r="B13" t="n">
-        <v>91813</v>
+        <v>57884</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1898,34 +1898,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560337</v>
+        <v>560355</v>
       </c>
       <c r="R13" t="n">
-        <v>6913867</v>
+        <v>6914099</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,7 +1965,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1967,7 +1975,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1994,53 +2007,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131328313</v>
+        <v>131328329</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>91777</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560355</v>
+        <v>560472</v>
       </c>
       <c r="R14" t="n">
-        <v>6914099</v>
+        <v>6913901</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2072,7 +2077,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2082,12 +2087,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,32 +2114,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131328329</v>
+        <v>131328326</v>
       </c>
       <c r="B15" t="n">
-        <v>91776</v>
+        <v>92273</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2149,10 +2149,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560472</v>
+        <v>560334</v>
       </c>
       <c r="R15" t="n">
-        <v>6913901</v>
+        <v>6913871</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2221,32 +2221,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131328326</v>
+        <v>131328332</v>
       </c>
       <c r="B16" t="n">
-        <v>92272</v>
+        <v>80351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560334</v>
+        <v>560517</v>
       </c>
       <c r="R16" t="n">
-        <v>6913871</v>
+        <v>6913922</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2328,10 +2328,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131328332</v>
+        <v>131328333</v>
       </c>
       <c r="B17" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2363,10 +2363,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560517</v>
+        <v>560530</v>
       </c>
       <c r="R17" t="n">
-        <v>6913922</v>
+        <v>6913912</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2435,10 +2435,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131328333</v>
+        <v>131328316</v>
       </c>
       <c r="B18" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2446,34 +2446,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560530</v>
+        <v>560442</v>
       </c>
       <c r="R18" t="n">
-        <v>6913912</v>
+        <v>6914020</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2505,7 +2513,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2515,7 +2523,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre bohål, dock fortfarande fjädrar kvar i öppningen. 2 meter ovam mark i grantickerötad död gran. Innerdiametern på hålet strax under 5 cm.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2542,10 +2555,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131328324</v>
+        <v>131328328</v>
       </c>
       <c r="B19" t="n">
-        <v>92232</v>
+        <v>91834</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2553,23 +2566,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6040186</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2577,10 +2586,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560334</v>
+        <v>560456</v>
       </c>
       <c r="R19" t="n">
-        <v>6913872</v>
+        <v>6913934</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2612,7 +2621,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2622,7 +2631,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2631,7 +2640,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2650,10 +2658,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131328316</v>
+        <v>131328335</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2661,42 +2669,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560442</v>
+        <v>560401</v>
       </c>
       <c r="R20" t="n">
-        <v>6914020</v>
+        <v>6913889</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2738,12 +2738,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre bohål, dock fortfarande fjädrar kvar i öppningen. 2 meter ovam mark i grantickerötad död gran. Innerdiametern på hålet strax under 5 cm.</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2770,41 +2765,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131328328</v>
+        <v>131328318</v>
       </c>
       <c r="B21" t="n">
-        <v>91833</v>
+        <v>5177</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560456</v>
+        <v>560288</v>
       </c>
       <c r="R21" t="n">
-        <v>6913934</v>
+        <v>6913825</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2836,7 +2844,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2846,7 +2854,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2855,6 +2863,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2873,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131328335</v>
+        <v>131328317</v>
       </c>
       <c r="B22" t="n">
-        <v>79245</v>
+        <v>57805</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2884,34 +2893,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100001</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560401</v>
+        <v>560426</v>
       </c>
       <c r="R22" t="n">
-        <v>6913889</v>
+        <v>6914014</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2943,7 +2956,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2953,14 +2966,19 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Större risbo i gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG22" t="b">
         <v>0</v>
@@ -2977,6 +2995,117 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131328324</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92233</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Getingtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>560334</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6913872</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51024-2024 artfynd.xlsx
+++ b/artfynd/A 51024-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131328338</v>
       </c>
       <c r="B2" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131328315</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>131328330</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>131328337</v>
       </c>
       <c r="B5" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>131328314</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>131328334</v>
       </c>
       <c r="B7" t="n">
-        <v>92536</v>
+        <v>92538</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>131328331</v>
       </c>
       <c r="B8" t="n">
-        <v>80386</v>
+        <v>80388</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>131328327</v>
       </c>
       <c r="B9" t="n">
-        <v>92038</v>
+        <v>92040</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>131328319</v>
       </c>
       <c r="B10" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>131328323</v>
       </c>
       <c r="B11" t="n">
-        <v>91810</v>
+        <v>91812</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>131328325</v>
       </c>
       <c r="B12" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,53 +1887,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131328313</v>
+        <v>131328329</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>91779</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560355</v>
+        <v>560472</v>
       </c>
       <c r="R13" t="n">
-        <v>6914099</v>
+        <v>6913901</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,7 +1957,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1975,12 +1967,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,45 +1994,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131328329</v>
+        <v>131328313</v>
       </c>
       <c r="B14" t="n">
-        <v>91777</v>
+        <v>57886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560472</v>
+        <v>560355</v>
       </c>
       <c r="R14" t="n">
-        <v>6913901</v>
+        <v>6914099</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,7 +2072,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2087,7 +2082,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,7 +2117,7 @@
         <v>131328326</v>
       </c>
       <c r="B15" t="n">
-        <v>92273</v>
+        <v>92275</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>131328332</v>
       </c>
       <c r="B16" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>131328333</v>
       </c>
       <c r="B17" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>131328316</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>131328328</v>
       </c>
       <c r="B19" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>131328335</v>
       </c>
       <c r="B20" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>131328317</v>
       </c>
       <c r="B22" t="n">
-        <v>57805</v>
+        <v>57807</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>131328324</v>
       </c>
       <c r="B23" t="n">
-        <v>92233</v>
+        <v>92235</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 51024-2024 artfynd.xlsx
+++ b/artfynd/A 51024-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131328338</v>
+        <v>131328315</v>
       </c>
       <c r="B2" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560289</v>
+        <v>560485</v>
       </c>
       <c r="R2" t="n">
-        <v>6914052</v>
+        <v>6914042</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131328315</v>
+        <v>131328330</v>
       </c>
       <c r="B3" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -828,7 +841,7 @@
         <v>560485</v>
       </c>
       <c r="R3" t="n">
-        <v>6914042</v>
+        <v>6913922</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +883,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131328330</v>
+        <v>131328338</v>
       </c>
       <c r="B4" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,42 +926,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560485</v>
+        <v>560289</v>
       </c>
       <c r="R4" t="n">
-        <v>6913922</v>
+        <v>6914052</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,12 +995,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131328337</v>
+        <v>131328314</v>
       </c>
       <c r="B5" t="n">
-        <v>91836</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,30 +1033,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560332</v>
+        <v>560365</v>
       </c>
       <c r="R5" t="n">
-        <v>6914009</v>
+        <v>6914101</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1098,7 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131328314</v>
+        <v>131328337</v>
       </c>
       <c r="B6" t="n">
-        <v>57886</v>
+        <v>91837</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1136,42 +1153,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560365</v>
+        <v>560332</v>
       </c>
       <c r="R6" t="n">
-        <v>6914101</v>
+        <v>6914009</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,12 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,7 +1248,7 @@
         <v>131328334</v>
       </c>
       <c r="B7" t="n">
-        <v>92538</v>
+        <v>92539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>131328331</v>
       </c>
       <c r="B8" t="n">
-        <v>80388</v>
+        <v>80389</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>131328327</v>
       </c>
       <c r="B9" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>131328319</v>
       </c>
       <c r="B10" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>131328323</v>
       </c>
       <c r="B11" t="n">
-        <v>91812</v>
+        <v>91813</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>131328325</v>
       </c>
       <c r="B12" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>131328329</v>
       </c>
       <c r="B13" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>131328313</v>
       </c>
       <c r="B14" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>131328326</v>
       </c>
       <c r="B15" t="n">
-        <v>92275</v>
+        <v>92276</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>131328332</v>
       </c>
       <c r="B16" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>131328333</v>
       </c>
       <c r="B17" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>131328316</v>
       </c>
       <c r="B18" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>131328328</v>
       </c>
       <c r="B19" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>131328335</v>
       </c>
       <c r="B20" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>131328317</v>
       </c>
       <c r="B22" t="n">
-        <v>57807</v>
+        <v>57808</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>131328324</v>
       </c>
       <c r="B23" t="n">
-        <v>92235</v>
+        <v>92236</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 51024-2024 artfynd.xlsx
+++ b/artfynd/A 51024-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131328315</v>
+        <v>131328338</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560485</v>
+        <v>560289</v>
       </c>
       <c r="R2" t="n">
-        <v>6914042</v>
+        <v>6914052</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:03</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -915,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131328338</v>
+        <v>131328315</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,34 +913,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560289</v>
+        <v>560485</v>
       </c>
       <c r="R4" t="n">
-        <v>6914052</v>
+        <v>6914042</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,7 +990,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1352,32 +1352,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131328331</v>
+        <v>131328327</v>
       </c>
       <c r="B8" t="n">
-        <v>80389</v>
+        <v>92041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>1106</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560515</v>
+        <v>560376</v>
       </c>
       <c r="R8" t="n">
-        <v>6913926</v>
+        <v>6913905</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,32 +1459,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131328327</v>
+        <v>131328331</v>
       </c>
       <c r="B9" t="n">
-        <v>92041</v>
+        <v>80389</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1106</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560376</v>
+        <v>560515</v>
       </c>
       <c r="R9" t="n">
-        <v>6913905</v>
+        <v>6913926</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2221,7 +2221,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131328332</v>
+        <v>131328333</v>
       </c>
       <c r="B16" t="n">
         <v>80354</v>
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560517</v>
+        <v>560530</v>
       </c>
       <c r="R16" t="n">
-        <v>6913922</v>
+        <v>6913912</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2328,7 +2328,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131328333</v>
+        <v>131328332</v>
       </c>
       <c r="B17" t="n">
         <v>80354</v>
@@ -2363,10 +2363,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560530</v>
+        <v>560517</v>
       </c>
       <c r="R17" t="n">
-        <v>6913912</v>
+        <v>6913922</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 51024-2024 artfynd.xlsx
+++ b/artfynd/A 51024-2024 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131328330</v>
+        <v>131328315</v>
       </c>
       <c r="B3" t="n">
         <v>57887</v>
@@ -828,7 +828,7 @@
         <v>560485</v>
       </c>
       <c r="R3" t="n">
-        <v>6913922</v>
+        <v>6914042</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +870,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131328315</v>
+        <v>131328330</v>
       </c>
       <c r="B4" t="n">
         <v>57887</v>
@@ -948,7 +948,7 @@
         <v>560485</v>
       </c>
       <c r="R4" t="n">
-        <v>6914042</v>
+        <v>6913922</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1352,32 +1352,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131328327</v>
+        <v>131328331</v>
       </c>
       <c r="B8" t="n">
-        <v>92041</v>
+        <v>80389</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1106</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560376</v>
+        <v>560515</v>
       </c>
       <c r="R8" t="n">
-        <v>6913905</v>
+        <v>6913926</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,32 +1459,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131328331</v>
+        <v>131328327</v>
       </c>
       <c r="B9" t="n">
-        <v>80389</v>
+        <v>92041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>1106</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560515</v>
+        <v>560376</v>
       </c>
       <c r="R9" t="n">
-        <v>6913926</v>
+        <v>6913905</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 51024-2024 artfynd.xlsx
+++ b/artfynd/A 51024-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131328315</v>
+        <v>131328338</v>
       </c>
       <c r="B2" t="n">
-        <v>57892</v>
+        <v>79260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560485</v>
+        <v>560289</v>
       </c>
       <c r="R2" t="n">
-        <v>6914042</v>
+        <v>6914052</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:03</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131328330</v>
+        <v>131328315</v>
       </c>
       <c r="B3" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,7 +828,7 @@
         <v>560485</v>
       </c>
       <c r="R3" t="n">
-        <v>6913922</v>
+        <v>6914042</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,12 +870,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131328338</v>
+        <v>131328330</v>
       </c>
       <c r="B4" t="n">
-        <v>79254</v>
+        <v>57898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,34 +913,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560289</v>
+        <v>560485</v>
       </c>
       <c r="R4" t="n">
-        <v>6914052</v>
+        <v>6913922</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,7 +990,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,7 +1025,7 @@
         <v>131328337</v>
       </c>
       <c r="B5" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>131328314</v>
       </c>
       <c r="B6" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>131328334</v>
       </c>
       <c r="B7" t="n">
-        <v>92544</v>
+        <v>92550</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>131328327</v>
       </c>
       <c r="B8" t="n">
-        <v>92046</v>
+        <v>92052</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>131328331</v>
       </c>
       <c r="B9" t="n">
-        <v>80394</v>
+        <v>80400</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131328323</v>
+        <v>131328319</v>
       </c>
       <c r="B10" t="n">
-        <v>91818</v>
+        <v>91828</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560332</v>
+        <v>560290</v>
       </c>
       <c r="R10" t="n">
-        <v>6913869</v>
+        <v>6913825</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,10 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131328319</v>
+        <v>131328323</v>
       </c>
       <c r="B11" t="n">
-        <v>91822</v>
+        <v>91824</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1684,21 +1684,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560290</v>
+        <v>560332</v>
       </c>
       <c r="R11" t="n">
-        <v>6913825</v>
+        <v>6913869</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,7 +1783,7 @@
         <v>131328325</v>
       </c>
       <c r="B12" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,45 +1887,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131328329</v>
+        <v>131328313</v>
       </c>
       <c r="B13" t="n">
-        <v>91785</v>
+        <v>57898</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560472</v>
+        <v>560355</v>
       </c>
       <c r="R13" t="n">
-        <v>6913901</v>
+        <v>6914099</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,7 +1965,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1967,7 +1975,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1994,53 +2007,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131328313</v>
+        <v>131328329</v>
       </c>
       <c r="B14" t="n">
-        <v>57892</v>
+        <v>91791</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560355</v>
+        <v>560472</v>
       </c>
       <c r="R14" t="n">
-        <v>6914099</v>
+        <v>6913901</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2072,7 +2077,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2082,12 +2087,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,7 +2117,7 @@
         <v>131328326</v>
       </c>
       <c r="B15" t="n">
-        <v>92281</v>
+        <v>92287</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,10 +2221,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131328332</v>
+        <v>131328333</v>
       </c>
       <c r="B16" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560517</v>
+        <v>560530</v>
       </c>
       <c r="R16" t="n">
-        <v>6913922</v>
+        <v>6913912</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2328,10 +2328,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131328333</v>
+        <v>131328332</v>
       </c>
       <c r="B17" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2363,10 +2363,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560530</v>
+        <v>560517</v>
       </c>
       <c r="R17" t="n">
-        <v>6913912</v>
+        <v>6913922</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2438,7 +2438,7 @@
         <v>131328316</v>
       </c>
       <c r="B18" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>131328328</v>
       </c>
       <c r="B19" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>131328335</v>
       </c>
       <c r="B20" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>131328317</v>
       </c>
       <c r="B22" t="n">
-        <v>57813</v>
+        <v>57819</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>131328324</v>
       </c>
       <c r="B23" t="n">
-        <v>92241</v>
+        <v>92247</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 51024-2024 artfynd.xlsx
+++ b/artfynd/A 51024-2024 artfynd.xlsx
@@ -1022,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131328337</v>
+        <v>131328314</v>
       </c>
       <c r="B5" t="n">
-        <v>91848</v>
+        <v>57898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,30 +1033,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560332</v>
+        <v>560365</v>
       </c>
       <c r="R5" t="n">
-        <v>6914009</v>
+        <v>6914101</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1098,7 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131328314</v>
+        <v>131328337</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>91848</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1136,42 +1153,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560365</v>
+        <v>560332</v>
       </c>
       <c r="R6" t="n">
-        <v>6914101</v>
+        <v>6914009</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,12 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1352,32 +1352,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131328327</v>
+        <v>131328331</v>
       </c>
       <c r="B8" t="n">
-        <v>92052</v>
+        <v>80400</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1106</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560376</v>
+        <v>560515</v>
       </c>
       <c r="R8" t="n">
-        <v>6913905</v>
+        <v>6913926</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,32 +1459,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131328331</v>
+        <v>131328327</v>
       </c>
       <c r="B9" t="n">
-        <v>80400</v>
+        <v>92052</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>1106</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560515</v>
+        <v>560376</v>
       </c>
       <c r="R9" t="n">
-        <v>6913926</v>
+        <v>6913905</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1887,53 +1887,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131328313</v>
+        <v>131328329</v>
       </c>
       <c r="B13" t="n">
-        <v>57898</v>
+        <v>91791</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560355</v>
+        <v>560472</v>
       </c>
       <c r="R13" t="n">
-        <v>6914099</v>
+        <v>6913901</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,7 +1957,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1975,12 +1967,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,45 +1994,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131328329</v>
+        <v>131328313</v>
       </c>
       <c r="B14" t="n">
-        <v>91791</v>
+        <v>57898</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560472</v>
+        <v>560355</v>
       </c>
       <c r="R14" t="n">
-        <v>6913901</v>
+        <v>6914099</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,7 +2072,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2087,7 +2082,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 51024-2024 artfynd.xlsx
+++ b/artfynd/A 51024-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131328338</v>
+        <v>131328315</v>
       </c>
       <c r="B2" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560289</v>
+        <v>560485</v>
       </c>
       <c r="R2" t="n">
-        <v>6914052</v>
+        <v>6914042</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131328315</v>
+        <v>131328330</v>
       </c>
       <c r="B3" t="n">
         <v>57898</v>
@@ -828,7 +841,7 @@
         <v>560485</v>
       </c>
       <c r="R3" t="n">
-        <v>6914042</v>
+        <v>6913922</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +883,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131328330</v>
+        <v>131328338</v>
       </c>
       <c r="B4" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,42 +926,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560485</v>
+        <v>560289</v>
       </c>
       <c r="R4" t="n">
-        <v>6913922</v>
+        <v>6914052</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,12 +995,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131328314</v>
+        <v>131328337</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>91848</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,42 +1033,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560365</v>
+        <v>560332</v>
       </c>
       <c r="R5" t="n">
-        <v>6914101</v>
+        <v>6914009</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1088,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1098,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131328337</v>
+        <v>131328314</v>
       </c>
       <c r="B6" t="n">
-        <v>91848</v>
+        <v>57898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,30 +1136,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560332</v>
+        <v>560365</v>
       </c>
       <c r="R6" t="n">
-        <v>6914009</v>
+        <v>6914101</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1213,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2221,7 +2221,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131328333</v>
+        <v>131328332</v>
       </c>
       <c r="B16" t="n">
         <v>80365</v>
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560530</v>
+        <v>560517</v>
       </c>
       <c r="R16" t="n">
-        <v>6913912</v>
+        <v>6913922</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2328,7 +2328,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131328332</v>
+        <v>131328333</v>
       </c>
       <c r="B17" t="n">
         <v>80365</v>
@@ -2363,10 +2363,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560517</v>
+        <v>560530</v>
       </c>
       <c r="R17" t="n">
-        <v>6913922</v>
+        <v>6913912</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 51024-2024 artfynd.xlsx
+++ b/artfynd/A 51024-2024 artfynd.xlsx
@@ -1248,7 +1248,7 @@
         <v>131328334</v>
       </c>
       <c r="B7" t="n">
-        <v>92550</v>
+        <v>92551</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,32 +1352,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131328331</v>
+        <v>131328327</v>
       </c>
       <c r="B8" t="n">
-        <v>80400</v>
+        <v>92053</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>1106</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560515</v>
+        <v>560376</v>
       </c>
       <c r="R8" t="n">
-        <v>6913926</v>
+        <v>6913905</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,32 +1459,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131328327</v>
+        <v>131328331</v>
       </c>
       <c r="B9" t="n">
-        <v>92052</v>
+        <v>80400</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1106</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560376</v>
+        <v>560515</v>
       </c>
       <c r="R9" t="n">
-        <v>6913905</v>
+        <v>6913926</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2117,7 +2117,7 @@
         <v>131328326</v>
       </c>
       <c r="B15" t="n">
-        <v>92287</v>
+        <v>92288</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>131328324</v>
       </c>
       <c r="B23" t="n">
-        <v>92247</v>
+        <v>92248</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 51024-2024 artfynd.xlsx
+++ b/artfynd/A 51024-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131328315</v>
+        <v>131328338</v>
       </c>
       <c r="B2" t="n">
-        <v>57898</v>
+        <v>79261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560485</v>
+        <v>560289</v>
       </c>
       <c r="R2" t="n">
-        <v>6914042</v>
+        <v>6914052</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:03</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131328330</v>
+        <v>131328315</v>
       </c>
       <c r="B3" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,7 +828,7 @@
         <v>560485</v>
       </c>
       <c r="R3" t="n">
-        <v>6913922</v>
+        <v>6914042</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,12 +870,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131328338</v>
+        <v>131328330</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,34 +913,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560289</v>
+        <v>560485</v>
       </c>
       <c r="R4" t="n">
-        <v>6914052</v>
+        <v>6913922</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,7 +990,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,7 +1025,7 @@
         <v>131328337</v>
       </c>
       <c r="B5" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>131328314</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>131328334</v>
       </c>
       <c r="B7" t="n">
-        <v>92551</v>
+        <v>92552</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,32 +1352,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131328327</v>
+        <v>131328331</v>
       </c>
       <c r="B8" t="n">
-        <v>92053</v>
+        <v>80401</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1106</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560376</v>
+        <v>560515</v>
       </c>
       <c r="R8" t="n">
-        <v>6913905</v>
+        <v>6913926</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,32 +1459,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131328331</v>
+        <v>131328327</v>
       </c>
       <c r="B9" t="n">
-        <v>80400</v>
+        <v>92054</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>1106</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560515</v>
+        <v>560376</v>
       </c>
       <c r="R9" t="n">
-        <v>6913926</v>
+        <v>6913905</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,7 +1569,7 @@
         <v>131328319</v>
       </c>
       <c r="B10" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>131328323</v>
       </c>
       <c r="B11" t="n">
-        <v>91824</v>
+        <v>91825</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>131328325</v>
       </c>
       <c r="B12" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,45 +1887,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131328329</v>
+        <v>131328313</v>
       </c>
       <c r="B13" t="n">
-        <v>91791</v>
+        <v>57899</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560472</v>
+        <v>560355</v>
       </c>
       <c r="R13" t="n">
-        <v>6913901</v>
+        <v>6914099</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,7 +1965,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1967,7 +1975,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1994,53 +2007,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131328313</v>
+        <v>131328329</v>
       </c>
       <c r="B14" t="n">
-        <v>57898</v>
+        <v>91792</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560355</v>
+        <v>560472</v>
       </c>
       <c r="R14" t="n">
-        <v>6914099</v>
+        <v>6913901</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2072,7 +2077,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2082,12 +2087,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,7 +2117,7 @@
         <v>131328326</v>
       </c>
       <c r="B15" t="n">
-        <v>92288</v>
+        <v>92289</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>131328332</v>
       </c>
       <c r="B16" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>131328333</v>
       </c>
       <c r="B17" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>131328316</v>
       </c>
       <c r="B18" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>131328328</v>
       </c>
       <c r="B19" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>131328335</v>
       </c>
       <c r="B20" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>131328318</v>
       </c>
       <c r="B21" t="n">
-        <v>5177</v>
+        <v>5178</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>131328317</v>
       </c>
       <c r="B22" t="n">
-        <v>57819</v>
+        <v>57820</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>131328324</v>
       </c>
       <c r="B23" t="n">
-        <v>92248</v>
+        <v>92249</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 51024-2024 artfynd.xlsx
+++ b/artfynd/A 51024-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131328338</v>
       </c>
       <c r="B2" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131328315</v>
       </c>
       <c r="B3" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>131328330</v>
       </c>
       <c r="B4" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>131328337</v>
       </c>
       <c r="B5" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>131328314</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>131328334</v>
       </c>
       <c r="B7" t="n">
-        <v>92552</v>
+        <v>92555</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>131328331</v>
       </c>
       <c r="B8" t="n">
-        <v>80401</v>
+        <v>80404</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>131328327</v>
       </c>
       <c r="B9" t="n">
-        <v>92054</v>
+        <v>92057</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>131328319</v>
       </c>
       <c r="B10" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>131328323</v>
       </c>
       <c r="B11" t="n">
-        <v>91825</v>
+        <v>91828</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>131328325</v>
       </c>
       <c r="B12" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,53 +1887,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131328313</v>
+        <v>131328329</v>
       </c>
       <c r="B13" t="n">
-        <v>57899</v>
+        <v>91795</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560355</v>
+        <v>560472</v>
       </c>
       <c r="R13" t="n">
-        <v>6914099</v>
+        <v>6913901</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,7 +1957,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1975,12 +1967,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,45 +1994,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131328329</v>
+        <v>131328313</v>
       </c>
       <c r="B14" t="n">
-        <v>91792</v>
+        <v>57902</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560472</v>
+        <v>560355</v>
       </c>
       <c r="R14" t="n">
-        <v>6913901</v>
+        <v>6914099</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,7 +2072,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2087,7 +2082,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,7 +2117,7 @@
         <v>131328326</v>
       </c>
       <c r="B15" t="n">
-        <v>92289</v>
+        <v>92292</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>131328332</v>
       </c>
       <c r="B16" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>131328333</v>
       </c>
       <c r="B17" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>131328316</v>
       </c>
       <c r="B18" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>131328328</v>
       </c>
       <c r="B19" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>131328335</v>
       </c>
       <c r="B20" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>131328317</v>
       </c>
       <c r="B22" t="n">
-        <v>57820</v>
+        <v>57823</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>131328324</v>
       </c>
       <c r="B23" t="n">
-        <v>92249</v>
+        <v>92252</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 51024-2024 artfynd.xlsx
+++ b/artfynd/A 51024-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131328338</v>
+        <v>131328315</v>
       </c>
       <c r="B2" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560289</v>
+        <v>560485</v>
       </c>
       <c r="R2" t="n">
-        <v>6914052</v>
+        <v>6914042</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131328315</v>
+        <v>131328330</v>
       </c>
       <c r="B3" t="n">
         <v>57902</v>
@@ -828,7 +841,7 @@
         <v>560485</v>
       </c>
       <c r="R3" t="n">
-        <v>6914042</v>
+        <v>6913922</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +883,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131328330</v>
+        <v>131328338</v>
       </c>
       <c r="B4" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,42 +926,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560485</v>
+        <v>560289</v>
       </c>
       <c r="R4" t="n">
-        <v>6913922</v>
+        <v>6914052</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,12 +995,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 51024-2024 artfynd.xlsx
+++ b/artfynd/A 51024-2024 artfynd.xlsx
@@ -1887,45 +1887,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131328329</v>
+        <v>131328313</v>
       </c>
       <c r="B13" t="n">
-        <v>91795</v>
+        <v>57902</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560472</v>
+        <v>560355</v>
       </c>
       <c r="R13" t="n">
-        <v>6913901</v>
+        <v>6914099</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,7 +1965,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1967,7 +1975,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1994,53 +2007,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131328313</v>
+        <v>131328329</v>
       </c>
       <c r="B14" t="n">
-        <v>57902</v>
+        <v>91795</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560355</v>
+        <v>560472</v>
       </c>
       <c r="R14" t="n">
-        <v>6914099</v>
+        <v>6913901</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2072,7 +2077,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2082,12 +2087,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 51024-2024 artfynd.xlsx
+++ b/artfynd/A 51024-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131328315</v>
       </c>
       <c r="B2" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>131328330</v>
       </c>
       <c r="B3" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131328338</v>
       </c>
       <c r="B4" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>131328337</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>131328314</v>
       </c>
       <c r="B6" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>131328334</v>
       </c>
       <c r="B7" t="n">
-        <v>92555</v>
+        <v>92561</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,32 +1352,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131328331</v>
+        <v>131328327</v>
       </c>
       <c r="B8" t="n">
-        <v>80404</v>
+        <v>92063</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>1106</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560515</v>
+        <v>560376</v>
       </c>
       <c r="R8" t="n">
-        <v>6913926</v>
+        <v>6913905</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,32 +1459,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131328327</v>
+        <v>131328331</v>
       </c>
       <c r="B9" t="n">
-        <v>92057</v>
+        <v>80406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1106</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560376</v>
+        <v>560515</v>
       </c>
       <c r="R9" t="n">
-        <v>6913905</v>
+        <v>6913926</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,7 +1569,7 @@
         <v>131328319</v>
       </c>
       <c r="B10" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>131328323</v>
       </c>
       <c r="B11" t="n">
-        <v>91828</v>
+        <v>91834</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>131328325</v>
       </c>
       <c r="B12" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,53 +1887,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131328313</v>
+        <v>131328329</v>
       </c>
       <c r="B13" t="n">
-        <v>57902</v>
+        <v>91801</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560355</v>
+        <v>560472</v>
       </c>
       <c r="R13" t="n">
-        <v>6914099</v>
+        <v>6913901</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,7 +1957,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1975,12 +1967,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,45 +1994,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131328329</v>
+        <v>131328313</v>
       </c>
       <c r="B14" t="n">
-        <v>91795</v>
+        <v>57904</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560472</v>
+        <v>560355</v>
       </c>
       <c r="R14" t="n">
-        <v>6913901</v>
+        <v>6914099</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,7 +2072,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2087,7 +2082,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,7 +2117,7 @@
         <v>131328326</v>
       </c>
       <c r="B15" t="n">
-        <v>92292</v>
+        <v>92298</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>131328332</v>
       </c>
       <c r="B16" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>131328333</v>
       </c>
       <c r="B17" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>131328316</v>
       </c>
       <c r="B18" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>131328328</v>
       </c>
       <c r="B19" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>131328335</v>
       </c>
       <c r="B20" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>131328317</v>
       </c>
       <c r="B22" t="n">
-        <v>57823</v>
+        <v>57825</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>131328324</v>
       </c>
       <c r="B23" t="n">
-        <v>92252</v>
+        <v>92258</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 51024-2024 artfynd.xlsx
+++ b/artfynd/A 51024-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131328330</v>
+        <v>131328338</v>
       </c>
       <c r="B3" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,42 +806,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560485</v>
+        <v>560289</v>
       </c>
       <c r="R3" t="n">
-        <v>6913922</v>
+        <v>6914052</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,12 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131328338</v>
+        <v>131328330</v>
       </c>
       <c r="B4" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,34 +913,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560289</v>
+        <v>560485</v>
       </c>
       <c r="R4" t="n">
-        <v>6914052</v>
+        <v>6913922</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,7 +990,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1887,45 +1887,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131328329</v>
+        <v>131328313</v>
       </c>
       <c r="B13" t="n">
-        <v>91801</v>
+        <v>57904</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560472</v>
+        <v>560355</v>
       </c>
       <c r="R13" t="n">
-        <v>6913901</v>
+        <v>6914099</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,7 +1965,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1967,7 +1975,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1994,53 +2007,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131328313</v>
+        <v>131328329</v>
       </c>
       <c r="B14" t="n">
-        <v>57904</v>
+        <v>91801</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560355</v>
+        <v>560472</v>
       </c>
       <c r="R14" t="n">
-        <v>6914099</v>
+        <v>6913901</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2072,7 +2077,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2082,12 +2087,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
